--- a/DataTables/Datas/#Charactor.xlsx
+++ b/DataTables/Datas/#Charactor.xlsx
@@ -1106,7 +1106,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:6">
@@ -1120,7 +1120,7 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/#Charactor.xlsx
+++ b/DataTables/Datas/#Charactor.xlsx
@@ -1016,6 +1016,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="5" max="5" width="11.5" customWidth="1"/>
+    <col min="6" max="6" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">

--- a/DataTables/Datas/#Charactor.xlsx
+++ b/DataTables/Datas/#Charactor.xlsx
@@ -1096,7 +1096,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="1:6">
       <c r="B5">
         <v>1</v>
       </c>
@@ -1107,10 +1107,10 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="1:6">
       <c r="B6">
         <v>2</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>2</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/#Charactor.xlsx
+++ b/DataTables/Datas/#Charactor.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -48,6 +48,18 @@
     <t>survivalTime</t>
   </si>
   <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>Defense</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -82,6 +94,18 @@
   </si>
   <si>
     <t>生存时长</t>
+  </si>
+  <si>
+    <t>血</t>
+  </si>
+  <si>
+    <t>攻</t>
+  </si>
+  <si>
+    <t>防</t>
+  </si>
+  <si>
+    <t>速度</t>
   </si>
 </sst>
 </file>
@@ -1012,14 +1036,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1038,65 +1062,113 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:10">
       <c r="B5">
         <v>1</v>
       </c>
@@ -1109,8 +1181,20 @@
       <c r="F5">
         <v>10</v>
       </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:10">
       <c r="B6">
         <v>2</v>
       </c>
@@ -1122,6 +1206,44 @@
       </c>
       <c r="F6">
         <v>10</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:10">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/#Charactor.xlsx
+++ b/DataTables/Datas/#Charactor.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -60,6 +60,12 @@
     <t>Speed</t>
   </si>
   <si>
+    <t>AIName</t>
+  </si>
+  <si>
+    <t>AIParam</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -106,6 +112,12 @@
   </si>
   <si>
     <t>速度</t>
+  </si>
+  <si>
+    <t>ai名</t>
+  </si>
+  <si>
+    <t>ai参数</t>
   </si>
 </sst>
 </file>
@@ -271,7 +283,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -280,6 +292,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -465,12 +483,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -597,7 +630,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -609,120 +642,123 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1036,14 +1072,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1074,101 +1110,125 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
       <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="L2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:12">
       <c r="B5">
         <v>1</v>
       </c>
@@ -1194,7 +1254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:12">
       <c r="B6">
         <v>2</v>
       </c>
@@ -1220,7 +1280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:10">
+    <row r="7" customFormat="1" spans="1:12">
       <c r="B7">
         <v>3</v>
       </c>

--- a/DataTables/Datas/#Charactor.xlsx
+++ b/DataTables/Datas/#Charactor.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -63,9 +63,6 @@
     <t>AIName</t>
   </si>
   <si>
-    <t>AIParam</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -117,7 +114,10 @@
     <t>ai名</t>
   </si>
   <si>
-    <t>ai参数</t>
+    <t>NormalMonster</t>
+  </si>
+  <si>
+    <t>EliteMonster</t>
   </si>
 </sst>
 </file>
@@ -1077,6 +1077,7 @@
   <cols>
     <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
+    <col min="11" max="11" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1113,120 +1114,112 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>23</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>24</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>25</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>26</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12">
       <c r="B5">
@@ -1279,6 +1272,9 @@
       <c r="J6">
         <v>5</v>
       </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="7" customFormat="1" spans="1:12">
       <c r="B7">
@@ -1304,6 +1300,9 @@
       </c>
       <c r="J7">
         <v>5</v>
+      </c>
+      <c r="K7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
